--- a/banco_tabajara.xlsx
+++ b/banco_tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,16 +447,6 @@
           <t>extrato</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Agencia</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Extrato</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -464,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chuck norris</t>
+          <t>wellington</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12345678956</t>
+          <t>02413390731</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -477,153 +467,11 @@
           <t>corrente</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="E2" t="n">
         <v>400</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rambo</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>12345678956</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>corrente</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>401</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VAN DAME</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>12345678963</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CORRENTE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>402</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>JUNIFL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12345678925</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CORRENTE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>403</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>wellington</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>02413390731</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>corrente</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>404</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>wellington</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>02413390731</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>corrente</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>405</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
+      <c r="F2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
